--- a/currentbuild/ValueSet-healthcare-person-id-type-vs.xlsx
+++ b/currentbuild/ValueSet-healthcare-person-id-type-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.6</t>
+    <t>0.1.7</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T12:03:39+00:00</t>
+    <t>2026-04-16T08:13:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
